--- a/dataset_t6_grouped/results2/G1/G1_T6020_W0056F0003T0006Z000C1N29_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T6020_W0056F0003T0006Z000C1N29_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>29.40400594393834</v>
+        <v>4.778150965889981</v>
       </c>
       <c r="D2" t="n">
-        <v>14.82975897964539</v>
+        <v>2.409835834192377</v>
       </c>
       <c r="E2" t="n">
-        <v>8.636922518037217</v>
+        <v>1.403499909181048</v>
       </c>
       <c r="F2" t="n">
-        <v>2.132785236539287</v>
+        <v>0.3465776009376341</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>12.00084010431424</v>
+        <v>1.950136516951063</v>
       </c>
       <c r="D3" t="n">
-        <v>13.05634149279675</v>
+        <v>2.121655492579472</v>
       </c>
       <c r="E3" t="n">
-        <v>8.636922518037217</v>
+        <v>1.403499909181048</v>
       </c>
       <c r="F3" t="n">
-        <v>2.132785236539287</v>
+        <v>0.3465776009376341</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>11.60635748195194</v>
+        <v>1.88603309081719</v>
       </c>
       <c r="D4" t="n">
-        <v>15.93369689485693</v>
+        <v>2.589225745414251</v>
       </c>
       <c r="E4" t="n">
-        <v>8.636922518037217</v>
+        <v>1.403499909181048</v>
       </c>
       <c r="F4" t="n">
-        <v>2.132785236539287</v>
+        <v>0.3465776009376341</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>6.607448417714959</v>
+        <v>1.073710367878681</v>
       </c>
       <c r="D5" t="n">
-        <v>10.28906835850314</v>
+        <v>1.67197360825676</v>
       </c>
       <c r="E5" t="n">
-        <v>8.636922518037217</v>
+        <v>1.403499909181048</v>
       </c>
       <c r="F5" t="n">
-        <v>2.132785236539287</v>
+        <v>0.3465776009376341</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
